--- a/data/GPS/Metricas_GPS (2).xlsx
+++ b/data/GPS/Metricas_GPS (2).xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30405"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E1D0ED-B08D-4892-BF23-156117DBAC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="_ib" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="_synced_data" sheetId="2" r:id="rId6"/>
+    <sheet name="_ib" sheetId="1" r:id="rId1"/>
+    <sheet name="_synced_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>eJy9lltv0zAUx7+KlSeQqjTNIEQIIRWqvbCVbmgb46LJtd3Gqy9RbK9bq353bLeMJLRlDVqeknNyfM7vf3zLMsBQExW8BctAS/9wDvsSxFGcRGmUBB0Q3EHmXMzF6mBlPZNC8qeGu/j8TqPJ1BX6vtwYNxS7KG4MhguapHM3FEm2CbJvm4iFmFP3LYc6c7YvaW39kJOyLSD39jFBGXQOI6h2DkdcTsgiq9V+p+pm6uknkCliHQXBBvkcWmpfAk4xmayH9ZKkF1sfEYZbj8f8WcLKpQpJjspkdniZg1NR5hyYAiIqRR3vGJ5dlvX6+FLWnMEHUpQzDSUfF2Sf5G/n8cegCku1q70378hGoU3UrsyYmtutzRwXRmXksU3/3VtM1Z7ezniltVRpKBCFwBazq7HG/Cm7SivMujDPgbwQJHzVEPw96KVgxrtZHf4kMVlb8ElDeEsfv+7EYKuAz/zitC0BbxoKcP2P0066XcGZhPftTQESeo+Cyjnww0TRGIIveUGFVuDFuz+z8PKvdSQ+9NsQARFyOuIGOvqIMLI+JC1Qjb93/rWVTYxJY/4BUXCfhIuhuj7s7OTrhddgDsLfQ3fcTV3VVWUNfRSCU3hPOaxToxHBB1KvL75G1FQcQj0gO7HzydFRK81WOf5Hs91+rFy0lx66TjyIr4fPfrXSWxUyiZ+4skf+HwGcSIiDlUuDGCVCr0sJw5h3Pu4DMgdXspiNpZwFq19ONxAM</t>
   </si>
@@ -86,18 +95,12 @@
     <t>Defensa Central</t>
   </si>
   <si>
-    <t xml:space="preserve">Rodri_Sanchez_Ramos </t>
-  </si>
-  <si>
     <t>Mediapunta</t>
   </si>
   <si>
     <t xml:space="preserve">Petko_Avramov </t>
   </si>
   <si>
-    <t xml:space="preserve">Carlos_De_La_Fe_Simon </t>
-  </si>
-  <si>
     <t xml:space="preserve">Guillermo_Garcia_Lapena </t>
   </si>
   <si>
@@ -132,12 +135,6 @@
   </si>
   <si>
     <t>Delantero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan_Manuel_Ruiz </t>
-  </si>
-  <si>
-    <t>Denfensa Lateral</t>
   </si>
   <si>
     <t xml:space="preserve">Noah_Ojo_Barranco </t>
@@ -146,25 +143,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -175,38 +173,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -214,7 +217,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -404,22 +407,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -428,21 +434,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="7" width="22.25"/>
+    <col min="6" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -489,12 +496,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B2" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>18</v>
@@ -506,42 +513,42 @@
         <v>7.04</v>
       </c>
       <c r="F2" s="2">
-        <v>0.391</v>
+        <v>0.39100000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>0.021</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="H2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="K2" s="2">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="L2" s="2">
-        <v>4.677</v>
+        <v>4.6769999999999996</v>
       </c>
       <c r="M2" s="2">
         <v>-4.8</v>
       </c>
       <c r="N2" s="2">
-        <v>28.228</v>
+        <v>28.228000000000002</v>
       </c>
       <c r="O2" s="2">
         <v>419.3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B3" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -550,45 +557,45 @@
         <v>21</v>
       </c>
       <c r="E3" s="2">
-        <v>6.182</v>
+        <v>6.1820000000000004</v>
       </c>
       <c r="F3" s="2">
         <v>0.504</v>
       </c>
       <c r="G3" s="2">
-        <v>0.047</v>
+        <v>4.7E-2</v>
       </c>
       <c r="H3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J3" s="2">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="K3" s="2">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="L3" s="2">
-        <v>4.563</v>
+        <v>4.5629999999999997</v>
       </c>
       <c r="M3" s="2">
         <v>-5.93</v>
       </c>
       <c r="N3" s="2">
-        <v>27.806</v>
+        <v>27.806000000000001</v>
       </c>
       <c r="O3" s="2">
         <v>1508.4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B4" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -597,745 +604,604 @@
         <v>23</v>
       </c>
       <c r="E4" s="2">
-        <v>5.837</v>
+        <v>5.8369999999999997</v>
       </c>
       <c r="F4" s="2">
-        <v>0.229</v>
+        <v>0.22900000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="K4" s="2">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="L4" s="2">
-        <v>5.046</v>
+        <v>5.0460000000000003</v>
       </c>
       <c r="M4" s="2">
         <v>-5.085</v>
       </c>
       <c r="N4" s="2">
-        <v>28.152</v>
+        <v>28.152000000000001</v>
       </c>
       <c r="O4" s="2">
         <v>1261.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B5" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0</v>
+        <v>6.3470000000000004</v>
       </c>
       <c r="F5" s="2">
-        <v>0.0</v>
+        <v>0.224</v>
       </c>
       <c r="G5" s="2">
-        <v>0.0</v>
+        <v>1.2E-2</v>
       </c>
       <c r="H5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>0.0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="2">
-        <v>0.0</v>
+        <v>47</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0</v>
+        <v>37</v>
       </c>
       <c r="L5" s="2">
-        <v>0.0</v>
+        <v>5.2770000000000001</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0</v>
+        <v>-6.1660000000000004</v>
       </c>
       <c r="N5" s="2">
-        <v>0.0</v>
+        <v>27.263000000000002</v>
       </c>
       <c r="O5" s="2">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>986.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B6" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2">
-        <v>6.347</v>
+        <v>6.3730000000000002</v>
       </c>
       <c r="F6" s="2">
-        <v>0.224</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="G6" s="2">
-        <v>0.012</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="H6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2">
-        <v>47.0</v>
+        <v>57</v>
       </c>
       <c r="K6" s="2">
-        <v>37.0</v>
+        <v>41</v>
       </c>
       <c r="L6" s="2">
-        <v>5.277</v>
+        <v>4.806</v>
       </c>
       <c r="M6" s="2">
-        <v>-6.166</v>
+        <v>-5.48</v>
       </c>
       <c r="N6" s="2">
-        <v>27.263</v>
+        <v>27.875</v>
       </c>
       <c r="O6" s="2">
-        <v>986.5</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>1265.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B7" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2">
-        <v>0.0</v>
+        <v>5.5220000000000002</v>
       </c>
       <c r="F7" s="2">
-        <v>0.0</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="2">
-        <v>0.0</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="H7" s="2">
-        <v>0.0</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="I7" s="2">
-        <v>0.0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2">
-        <v>0.0</v>
+        <v>45</v>
       </c>
       <c r="K7" s="2">
-        <v>0.0</v>
+        <v>26</v>
       </c>
       <c r="L7" s="2">
-        <v>0.0</v>
+        <v>4.649</v>
       </c>
       <c r="M7" s="2">
-        <v>0.0</v>
+        <v>-6.9710000000000001</v>
       </c>
       <c r="N7" s="2">
-        <v>0.0</v>
+        <v>30.6</v>
       </c>
       <c r="O7" s="2">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>1254.4000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B8" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2">
-        <v>6.373</v>
+        <v>5.5060000000000002</v>
       </c>
       <c r="F8" s="2">
-        <v>0.281</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>0.013</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2">
-        <v>57.0</v>
+        <v>42</v>
       </c>
       <c r="K8" s="2">
-        <v>41.0</v>
+        <v>32</v>
       </c>
       <c r="L8" s="2">
-        <v>4.806</v>
+        <v>4.37</v>
       </c>
       <c r="M8" s="2">
-        <v>-5.48</v>
+        <v>-5.3780000000000001</v>
       </c>
       <c r="N8" s="2">
-        <v>27.875</v>
+        <v>27.544</v>
       </c>
       <c r="O8" s="2">
-        <v>1265.7</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>1314.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B9" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2">
-        <v>5.522</v>
+        <v>6.5119999999999996</v>
       </c>
       <c r="F9" s="2">
-        <v>0.2</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="G9" s="2">
-        <v>0.026</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="H9" s="2">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>2.0</v>
+        <v>3</v>
       </c>
       <c r="J9" s="2">
-        <v>45.0</v>
+        <v>57</v>
       </c>
       <c r="K9" s="2">
-        <v>26.0</v>
+        <v>58</v>
       </c>
       <c r="L9" s="2">
-        <v>4.649</v>
+        <v>5.1369999999999996</v>
       </c>
       <c r="M9" s="2">
-        <v>-6.971</v>
+        <v>-5.7080000000000002</v>
       </c>
       <c r="N9" s="2">
-        <v>30.6</v>
+        <v>28.094000000000001</v>
       </c>
       <c r="O9" s="2">
-        <v>1254.4</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>1137.9000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B10" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2">
-        <v>5.506</v>
+        <v>5.593</v>
       </c>
       <c r="F10" s="2">
-        <v>0.237</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="G10" s="2">
-        <v>0.018</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="H10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2">
-        <v>42.0</v>
+        <v>53</v>
       </c>
       <c r="K10" s="2">
-        <v>32.0</v>
+        <v>37</v>
       </c>
       <c r="L10" s="2">
-        <v>4.37</v>
+        <v>5.0430000000000001</v>
       </c>
       <c r="M10" s="2">
-        <v>-5.378</v>
+        <v>-5.6319999999999997</v>
       </c>
       <c r="N10" s="2">
-        <v>27.544</v>
+        <v>27.391999999999999</v>
       </c>
       <c r="O10" s="2">
-        <v>1314.2</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>1202.9000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B11" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E11" s="2">
-        <v>6.512</v>
+        <v>7.3010000000000002</v>
       </c>
       <c r="F11" s="2">
-        <v>0.348</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="G11" s="2">
-        <v>0.021</v>
+        <v>0.05</v>
       </c>
       <c r="H11" s="2">
-        <v>0.0</v>
+        <v>2E-3</v>
       </c>
       <c r="I11" s="2">
-        <v>3.0</v>
+        <v>7</v>
       </c>
       <c r="J11" s="2">
-        <v>57.0</v>
+        <v>55</v>
       </c>
       <c r="K11" s="2">
-        <v>58.0</v>
+        <v>49</v>
       </c>
       <c r="L11" s="2">
-        <v>5.137</v>
+        <v>4.851</v>
       </c>
       <c r="M11" s="2">
-        <v>-5.708</v>
+        <v>-6.3929999999999998</v>
       </c>
       <c r="N11" s="2">
-        <v>28.094</v>
+        <v>29.416</v>
       </c>
       <c r="O11" s="2">
-        <v>1137.9</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>1708.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B12" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2">
-        <v>5.593</v>
+        <v>6.1849999999999996</v>
       </c>
       <c r="F12" s="2">
-        <v>0.199</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="G12" s="2">
-        <v>0.013</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="H12" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="2">
-        <v>53.0</v>
+        <v>74</v>
       </c>
       <c r="K12" s="2">
-        <v>37.0</v>
+        <v>64</v>
       </c>
       <c r="L12" s="2">
-        <v>5.043</v>
+        <v>5.0369999999999999</v>
       </c>
       <c r="M12" s="2">
-        <v>-5.632</v>
+        <v>-5.3710000000000004</v>
       </c>
       <c r="N12" s="2">
-        <v>27.392</v>
+        <v>26.492000000000001</v>
       </c>
       <c r="O12" s="2">
-        <v>1202.9</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>1613.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B13" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E13" s="2">
-        <v>7.301</v>
+        <v>2.9460000000000002</v>
       </c>
       <c r="F13" s="2">
-        <v>0.593</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="G13" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H13" s="2">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>7.0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>55.0</v>
+        <v>15</v>
       </c>
       <c r="K13" s="2">
-        <v>49.0</v>
+        <v>9</v>
       </c>
       <c r="L13" s="2">
-        <v>4.851</v>
+        <v>3.9510000000000001</v>
       </c>
       <c r="M13" s="2">
-        <v>-6.393</v>
+        <v>-4.2619999999999996</v>
       </c>
       <c r="N13" s="2">
-        <v>29.416</v>
+        <v>23.417999999999999</v>
       </c>
       <c r="O13" s="2">
-        <v>1708.2</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>523.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B14" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2">
-        <v>6.185</v>
+        <v>5.6909999999999998</v>
       </c>
       <c r="F14" s="2">
-        <v>0.271</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="G14" s="2">
-        <v>0.008</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="H14" s="2">
-        <v>0.0</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="I14" s="2">
-        <v>2.0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="2">
-        <v>74.0</v>
+        <v>49</v>
       </c>
       <c r="K14" s="2">
-        <v>64.0</v>
+        <v>43</v>
       </c>
       <c r="L14" s="2">
-        <v>5.037</v>
+        <v>4.7610000000000001</v>
       </c>
       <c r="M14" s="2">
-        <v>-5.371</v>
+        <v>-5.6420000000000003</v>
       </c>
       <c r="N14" s="2">
-        <v>26.492</v>
+        <v>31.161999999999999</v>
       </c>
       <c r="O14" s="2">
-        <v>1613.2</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>1382.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B15" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2">
-        <v>2.946</v>
+        <v>5.125</v>
       </c>
       <c r="F15" s="2">
-        <v>0.095</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="G15" s="2">
-        <v>0.0</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="H15" s="2">
-        <v>0.0</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="I15" s="2">
-        <v>0.0</v>
+        <v>4</v>
       </c>
       <c r="J15" s="2">
-        <v>15.0</v>
+        <v>34</v>
       </c>
       <c r="K15" s="2">
-        <v>9.0</v>
+        <v>22</v>
       </c>
       <c r="L15" s="2">
-        <v>3.951</v>
+        <v>4.2060000000000004</v>
       </c>
       <c r="M15" s="2">
-        <v>-4.262</v>
+        <v>-4.8780000000000001</v>
       </c>
       <c r="N15" s="2">
-        <v>23.418</v>
+        <v>29.326000000000001</v>
       </c>
       <c r="O15" s="2">
-        <v>523.5</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>1070.9000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>46240.0</v>
+        <v>46240</v>
       </c>
       <c r="B16" s="2">
-        <v>91.055</v>
+        <v>91.055000000000007</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2">
-        <v>5.691</v>
+        <v>4.9359999999999999</v>
       </c>
       <c r="F16" s="2">
-        <v>0.367</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="G16" s="2">
-        <v>0.044</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="H16" s="2">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>5.0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="2">
-        <v>49.0</v>
+        <v>52</v>
       </c>
       <c r="K16" s="2">
-        <v>43.0</v>
+        <v>39</v>
       </c>
       <c r="L16" s="2">
-        <v>4.761</v>
+        <v>5.0579999999999998</v>
       </c>
       <c r="M16" s="2">
-        <v>-5.642</v>
+        <v>-5.7489999999999997</v>
       </c>
       <c r="N16" s="2">
-        <v>31.162</v>
+        <v>26.995999999999999</v>
       </c>
       <c r="O16" s="2">
-        <v>1382.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3">
-        <v>46240.0</v>
-      </c>
-      <c r="B17" s="2">
-        <v>91.055</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="2">
-        <v>5.125</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.278</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0.065</v>
-      </c>
-      <c r="H17" s="2">
-        <v>0.006</v>
-      </c>
-      <c r="I17" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="J17" s="2">
-        <v>34.0</v>
-      </c>
-      <c r="K17" s="2">
-        <v>22.0</v>
-      </c>
-      <c r="L17" s="2">
-        <v>4.206</v>
-      </c>
-      <c r="M17" s="2">
-        <v>-4.878</v>
-      </c>
-      <c r="N17" s="2">
-        <v>29.326</v>
-      </c>
-      <c r="O17" s="2">
-        <v>1070.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3">
-        <v>46240.0</v>
-      </c>
-      <c r="B18" s="2">
-        <v>91.055</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="O18" s="2">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3">
-        <v>46240.0</v>
-      </c>
-      <c r="B19" s="2">
-        <v>91.055</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="2">
-        <v>4.936</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.334</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0.008</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="J19" s="2">
-        <v>52.0</v>
-      </c>
-      <c r="K19" s="2">
-        <v>39.0</v>
-      </c>
-      <c r="L19" s="2">
-        <v>5.058</v>
-      </c>
-      <c r="M19" s="2">
-        <v>-5.749</v>
-      </c>
-      <c r="N19" s="2">
-        <v>26.996</v>
-      </c>
-      <c r="O19" s="2">
         <v>1267.5</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>